--- a/output/all_figures/Table3_cross_jurisdictional.xlsx
+++ b/output/all_figures/Table3_cross_jurisdictional.xlsx
@@ -461,17 +461,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Partial / encouraged</t>
+          <t>Recommended; not mandatory</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Recommended, not mandatory</t>
+          <t>Recommended; not mandatory</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Recommended for generalizability</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FDA PCCP Guidance (2023); FDA/Health Canada/MHRA GMLP principles</t>
+          <t>FDA AI lifecycle draft; FDA PCCP final guidance</t>
         </is>
       </c>
     </row>
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yes (2026 MLMD guidance)</t>
+          <t>Expected for MLMDs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Partial-to-Yes</t>
+          <t>Expected; risk-based</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>Multi-centre status described</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -518,12 +518,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Proposed / evolving</t>
+          <t>Yes; evolving</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Health Canada Pre-market Guidance for Machine Learning-enabled Medical Devices (2026)</t>
+          <t>Health Canada MLMD pre-market guidance</t>
         </is>
       </c>
     </row>
@@ -535,17 +535,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yes (high-risk systems)</t>
+          <t>Required for high-risk AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Required via representativeness</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Effectively expected via representativeness requirements</t>
+          <t>Not explicit; representativeness required</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -555,12 +555,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lifecycle monitoring + post-market surveillance</t>
+          <t>Post-market monitoring required</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EU AI Act Article 10 (Data and data governance)</t>
+          <t>EU AI Act Articles 10 and 72</t>
         </is>
       </c>
     </row>
@@ -572,32 +572,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Not explicitly required</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Not explicitly required</t>
+          <t>Not explicit</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Comparable to FDA approach</t>
+          <t>Comparable evidence allowed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under review / IMDRF-aligned</t>
+          <t>Under IMDRF-aligned review</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TGA AI-enabled medical device guidance; IMDRF SaMD framework</t>
+          <t>TGA AI software evidence guidance / PCCP consultation</t>
         </is>
       </c>
     </row>
@@ -609,32 +609,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Case-specific</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Limited / case-specific</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Not explicit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Limited</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Not explicitly required</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Limited</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pilot discussions (2024 onward)</t>
+          <t>PACMP/IDATEN available</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PMDA AI/ML medical device discussions; IMDRF SaMD principles</t>
+          <t>PMDA SaMD/QMS AI-SaMD documents</t>
         </is>
       </c>
     </row>
